--- a/docs/TestCases.xlsx
+++ b/docs/TestCases.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="End-to-End Workflow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Automated Run" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$J$138</definedName>
@@ -21,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="DD-MMM-YYYY"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +54,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -71,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -93,11 +100,25 @@
         <color rgb="00D9D2C5"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,6 +148,14 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -683,9 +712,9 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,9 +805,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Installer: run on the client PC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -816,9 +849,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr"/>
-      <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Installer: run on a PC without the engine</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -853,12 +890,22 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DatabaseInitializerTests.Initialize_UsesAnAccessDatabaseEngineProvider; MainFormTests.LoginForm_CanBeCreated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -893,12 +940,22 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DatabaseInitializerTests.Initialize_CreatesRequiredFolders; DatabaseInitializerTests.Initialize_CreatesDatabaseFileInDataFolder</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -933,12 +990,22 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Run the new setup over the installed version once. Passed: DatabaseInitializerTests.Initialize_RunAgain_KeepsExistingData</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -976,9 +1043,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Start menu shortcut on the client PC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1013,12 +1084,22 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Passed: MainFormTests.LoginForm_CanBeCreated; ScreenshotTests.LoginScreen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1053,12 +1134,22 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.NewDatabase_SignsInWithTheDefaultLogin; MainFormTests.MainForm_OpensEveryScreenFromTheMenu</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1093,12 +1184,22 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="11" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.InvalidLogin</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1133,12 +1234,22 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.NewDatabase_SignsInWithTheDefaultLogin</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1173,12 +1284,22 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.InvalidLogin</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1213,12 +1334,22 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Passed: MainFormTests.MainForm_ShowsSelectedHostelAndFollowsChanges; HostelServiceTests.HostelContext_SelectsRequestedOrFirstHostel</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1253,12 +1384,22 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.SaveContact_StoresEmailAndPhone</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1293,12 +1434,22 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.SaveContact_StoresEmailAndPhone</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1333,12 +1484,22 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.ChangePassword_TheNewPasswordWorksAndTheOldOneDoesNot; AuthServiceTests.Password_IsStoredAsASaltedHash</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -1373,12 +1534,22 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.ChangePassword_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1413,12 +1584,22 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.ChangePassword_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1453,12 +1634,22 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AuthServiceTests.ChangePassword_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1493,12 +1684,22 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Passed: HostelServiceTests.Save_AddsSeveralHostelsSortedByName; HostelServiceTests.Save_RaisesHostelsChanged</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -1533,12 +1734,22 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Passed: HostelServiceTests.Save_InvalidInput_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -1573,12 +1784,22 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Passed: HostelServiceTests.Save_DuplicateNameIgnoringCase_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -1613,12 +1834,22 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Passed: HostelServiceTests.Save_NewHostel_GetsItsOwnSingleDoubleTripleSharingTypes; ServiceItemServiceTests.NewHostel_HasWifiAndLaundryIncludedAndTransportExtra</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1653,12 +1884,22 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Passed: MainFormTests.StudentsAndParentsScreens_ShowTheHostelsData; RoomServiceTests.GetRooms_ShowsOnlyTheHostelsRooms; CollegeServiceTests.Search_ShowsOnlyTheHostelsColleges; PaymentServiceTests.GetPayments_ShowsOnlyTheHostelsPayments_NewestFirst</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -1693,12 +1934,22 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Passed: CollegeServiceTests.Save_AddsCollegeToTheHostel; CollegeServiceTests.Search_ShowsOnlyTheHostelsColleges</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -1733,12 +1984,22 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Passed: CollegeServiceTests.Save_DuplicateNameInSameHostelIgnoringCase_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1773,12 +2034,22 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Passed: CollegeServiceTests.Delete_CollegeWithStudents_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -1813,12 +2084,22 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr"/>
-      <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.UpdateRent_AppliesToEveryRoomOfThatSharingType; BillingPeriodsTests.InstallmentAmount_IsYearlyRentDividedByInstallments</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -1853,12 +2134,22 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr"/>
-      <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.UpdateRent_InvalidAmount_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1893,12 +2184,22 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Save_AddsRoomWithCapacityFromSharingType; RoomServiceTests.GetRooms_CountsOnlyCurrentAllocations</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -1933,12 +2234,22 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Save_DuplicateRoomNumberIgnoringCase_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -1973,12 +2284,22 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Save_RequiresBoysOrGirls</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -2013,12 +2334,22 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Edit_ChangingToSmallerSharingThanOccupancy_IsRejected; AgreementServiceTests.Room_CannotBecomeSmallerThanABedInUse</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -2053,12 +2384,22 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Edit_ChangingGenderOfOccupiedRoom_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -2093,12 +2434,22 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr"/>
-      <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Edit_DeactivatingOccupiedRoom_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -2133,12 +2484,22 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr"/>
-      <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Passed: RoomServiceTests.Delete_RoomNeverUsed_Succeeds; RoomServiceTests.Delete_RoomWithPastStudents_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -2173,12 +2534,22 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr"/>
-      <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ServiceItemServiceTests.Save_ExtraServiceNeedsAMonthlyRate_IncludedServiceHasNoCharge</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
@@ -2213,12 +2584,22 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr"/>
-      <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ServiceItemServiceTests.Save_ExtraServiceNeedsAMonthlyRate_IncludedServiceHasNoCharge; ServiceItemServiceTests.Save_DuplicateNameInHostel_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -2253,12 +2634,22 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr"/>
-      <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ServiceItemServiceTests.ServiceInUse_CannotBeDeactivatedMadeIncludedOrDeleted</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
@@ -2293,12 +2684,22 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr"/>
-      <c r="I40" s="11" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_AddsStudentWithPrimaryParent</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -2333,12 +2734,22 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
-      <c r="I41" s="11" t="inlineStr"/>
-      <c r="J41" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_StudentRequiredFields; StudentServiceTests.Save_RequiresCollege; StudentServiceTests.Save_ParentNameMobileAndEmailAreRequired</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -2373,12 +2784,22 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr"/>
-      <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ValidatorsTests.Email_Invalid; ValidatorsTests.Phone_Invalid; StudentServiceTests.Save_ParentNameMobileAndEmailAreRequired</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -2413,12 +2834,22 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr"/>
-      <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_InvalidAadhaar_IsRejected; StudentServiceTests.Save_DuplicateAadhaar_IsRejected; StudentServiceTests.Validators_Aadhaar</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -2453,12 +2884,22 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr"/>
-      <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_AddsStudentWithPrimaryParent; ReportServiceTests.StudentList_FiltersByStatusAndCollege_AndMasksAadhaar</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -2493,12 +2934,22 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr"/>
-      <c r="I45" s="11" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_StoresPhotoAndAadhaarCardUnderGeneratedNames; StudentServiceTests.Save_ReplacingOrRemovingFiles_DeletesTheOldFiles</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
@@ -2533,12 +2984,22 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
-      <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_InvalidFiles_AreRejectedBeforeAnythingIsSaved; StudentServiceTests.Save_FileLargerThan5MB_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -2573,12 +3034,22 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr"/>
-      <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ServiceItemServiceTests.NewStudent_ServiceStartsOnTheAdmissionDate; InvoiceServiceTests.Preview_TransportIsChargedPerMonth_PartMonthCountsAsFullMonth</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -2616,9 +3087,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr"/>
-      <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Type in the search box and use the filters on the Students screen</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -2653,12 +3128,22 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr"/>
-      <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Save_EditUpdatesStudentAndParent</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -2693,12 +3178,22 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr"/>
-      <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Passed: StudentServiceTests.Delete_StudentWithRoomHistory_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -2733,12 +3228,22 @@
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr"/>
-      <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ParentServiceTests.Save_AddsExtraGuardianAsSecondaryContact</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -2773,12 +3278,22 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr"/>
-      <c r="I52" s="11" t="inlineStr"/>
-      <c r="J52" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ParentServiceTests.Save_MarkingAnotherParentPrimary_ReplacesThePrimaryContact</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -2813,12 +3328,22 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr"/>
-      <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ParentServiceTests.Delete_OnlyParent_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -2853,12 +3378,22 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr"/>
-      <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.CheckIn_GivesTheLowestFreeBed_AndCheckOutFreesIt; AllocationServiceTests.CheckIn_PutsStudentInRoomAndCountsOccupancy</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -2893,12 +3428,22 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr"/>
-      <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.CheckIn_ChosenBed_MustBeFreeAndInTheRoom</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -2933,12 +3478,22 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr"/>
-      <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AllocationServiceTests.Lists_CurrentAllocationsHistoryStudentsWithoutRoomAndRoomsForGender; AllocationServiceTests.CheckIn_RoomOfOtherGender_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -2973,12 +3528,22 @@
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr"/>
-      <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AllocationServiceTests.CheckIn_FullRoom_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
@@ -3013,12 +3578,22 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr"/>
-      <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AllocationServiceTests.CheckIn_DatesAreChecked</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -3053,12 +3628,22 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr"/>
-      <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AllocationServiceTests.CheckIn_DatesAreChecked</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
@@ -3093,12 +3678,22 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr"/>
-      <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AllocationServiceTests.Transfer_LeavesOldRoomAndEntersNewRoomOnTheSameDay; AllocationServiceTests.Transfer_Rules; AgreementServiceTests.Transfer_GetsABedInTheNewRoom</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
@@ -3133,12 +3728,22 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr"/>
-      <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I61" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AllocationServiceTests.CheckOut_FreesTheBedAndSetsStudentToLeft; AllocationServiceTests.CheckOut_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -3176,9 +3781,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr"/>
-      <c r="I62" s="11" t="inlineStr"/>
-      <c r="J62" s="10" t="inlineStr"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Question box after check-in</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -3213,12 +3822,22 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr"/>
-      <c r="I63" s="11" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I63" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Open the PDF once to look at the layout. Passed: AgreementServiceTests.Prepare_FillsTheStudentParentAddressRoomBedAndFee; AgreementServiceTests.Pdf_IsWrittenOnSeveralPagesToTheAgreementsFolder; AgreementServiceTests.Words_MarkFilledValuesBold</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
@@ -3253,12 +3872,22 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr"/>
-      <c r="I64" s="11" t="inlineStr"/>
-      <c r="J64" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I64" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.Prepare_FillsTheStudentParentAddressRoomBedAndFee</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
@@ -3293,12 +3922,22 @@
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr"/>
-      <c r="I65" s="11" t="inlineStr"/>
-      <c r="J65" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I65" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.Prepare_GirlUsesDOAndGirlsHostel_MissingAddressLeavesADottedLine</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
@@ -3333,12 +3972,22 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr"/>
-      <c r="I66" s="11" t="inlineStr"/>
-      <c r="J66" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.Prepare_GirlUsesDOAndGirlsHostel_MissingAddressLeavesADottedLine</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
@@ -3373,12 +4022,22 @@
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr"/>
-      <c r="I67" s="11" t="inlineStr"/>
-      <c r="J67" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.Prepare_StudentWithoutRoom_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
@@ -3413,12 +4072,22 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr"/>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.Template_CanBeEditedAndRestored</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
@@ -3453,12 +4122,22 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr"/>
-      <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I69" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AgreementServiceTests.Template_CanBeEditedAndRestored</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
@@ -3493,12 +4172,22 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr"/>
-      <c r="I70" s="11" t="inlineStr"/>
-      <c r="J70" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AttendanceServiceTests.Sheet_ListsTheStudentsInARoomThatNight_AllPresentAtFirst</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
@@ -3533,12 +4222,22 @@
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr"/>
-      <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AttendanceServiceTests.Save_StoresAbsences_AndCanBeCorrectedLater; AttendanceServiceTests.View_MarkAbsentSaveAndListAbsent</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
@@ -3573,12 +4272,22 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr"/>
-      <c r="I72" s="11" t="inlineStr"/>
-      <c r="J72" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AttendanceServiceTests.Save_StoresAbsences_AndCanBeCorrectedLater</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
@@ -3613,12 +4322,22 @@
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr"/>
-      <c r="I73" s="11" t="inlineStr"/>
-      <c r="J73" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AttendanceServiceTests.Save_StoresAbsences_AndCanBeCorrectedLater</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -3653,12 +4372,22 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr"/>
-      <c r="I74" s="11" t="inlineStr"/>
-      <c r="J74" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AttendanceServiceTests.Save_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
@@ -3696,9 +4425,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr"/>
-      <c r="I75" s="11" t="inlineStr"/>
-      <c r="J75" s="10" t="inlineStr"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Question box when leaving unsaved changes</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
@@ -3733,12 +4466,22 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr"/>
-      <c r="I76" s="11" t="inlineStr"/>
-      <c r="J76" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>Passed: AttendanceServiceTests.Sheet_ListsTheStudentsInARoomThatNight_AllPresentAtFirst</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
@@ -3773,12 +4516,22 @@
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr"/>
-      <c r="I77" s="11" t="inlineStr"/>
-      <c r="J77" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I77" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Real delivery through Gmail. Passed: AttendanceServiceTests.AbsenceEmails_GoToTheParentsOfAbsentStudents_Once; EmailServiceTests.EveryEmail_IsCopiedToTheAdmin</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
@@ -3813,12 +4566,22 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr"/>
-      <c r="I78" s="11" t="inlineStr"/>
-      <c r="J78" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Question box before emailing again. Passed: AttendanceServiceTests.AbsenceEmails_GoToTheParentsOfAbsentStudents_Once</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
@@ -3853,12 +4616,22 @@
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
-      <c r="I79" s="11" t="inlineStr"/>
-      <c r="J79" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I79" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_RentIsHalfTheYearlyRent_IncludedServicesAtNoCharge; InvoiceServiceTests.Create_NumbersInvoicesPerAcademicYear</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
@@ -3893,12 +4666,22 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr"/>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_RentIsHalfTheYearlyRent_IncludedServicesAtNoCharge; InvoiceServiceTests.Preview_QuarterlyHostel_ChargesAQuarterOfTheYearlyRent</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
@@ -3933,12 +4716,22 @@
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr"/>
-      <c r="I81" s="11" t="inlineStr"/>
-      <c r="J81" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I81" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_StudentJoiningMidPeriod_PaysTheFullInstallment</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
@@ -3973,12 +4766,22 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
-      <c r="I82" s="11" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_TransportIsChargedPerMonth_PartMonthCountsAsFullMonth; InvoiceServiceTests.Preview_TransportStoppedMidPeriod_CountsOnlyTheMonthsUsed</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
@@ -4013,12 +4816,22 @@
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr"/>
-      <c r="I83" s="11" t="inlineStr"/>
-      <c r="J83" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I83" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
@@ -4053,12 +4866,22 @@
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr"/>
-      <c r="I84" s="11" t="inlineStr"/>
-      <c r="J84" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I84" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
@@ -4093,12 +4916,22 @@
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr"/>
-      <c r="I85" s="11" t="inlineStr"/>
-      <c r="J85" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I85" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Preview_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
@@ -4133,12 +4966,22 @@
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
-      <c r="I86" s="11" t="inlineStr"/>
-      <c r="J86" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I86" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Create_NumbersInvoicesPerAcademicYear; InvoiceServiceTests.AcademicYearLabel_StartsInJuly</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
@@ -4173,12 +5016,22 @@
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr"/>
-      <c r="I87" s="11" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I87" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Print once on the office printer. Passed: InvoiceServiceTests.Pdf_IsWrittenToTheInvoicesFolder; PendingDuesServiceTests.Invoice_IsDueFifteenDaysAfterItsDate_AndOverdueAfterThat</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
@@ -4213,12 +5066,22 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr"/>
-      <c r="I88" s="11" t="inlineStr"/>
-      <c r="J88" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PendingDuesServiceTests.Invoice_IsDueFifteenDaysAfterItsDate_AndOverdueAfterThat; InvoiceServiceTests.Invoices_ShowPaidPendingAndStatusFromPayments</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
@@ -4253,12 +5116,22 @@
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr"/>
-      <c r="I89" s="11" t="inlineStr"/>
-      <c r="J89" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I89" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Passed: InvoiceServiceTests.Delete_InvoiceWithoutPayments_RemovesItAndItsItems; PaymentServiceTests.Delete_MakesTheAmountPendingAgain_AndInvoiceCanThenBeDeleted</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
@@ -4293,12 +5166,22 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr"/>
-      <c r="I90" s="11" t="inlineStr"/>
-      <c r="J90" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Record_PartPayments_UpdateInvoicePaidPendingAndStatus; PaymentServiceTests.Record_NumbersReceiptsPerAcademicYearOfThePaymentDate</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
@@ -4333,12 +5216,22 @@
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr"/>
-      <c r="I91" s="11" t="inlineStr"/>
-      <c r="J91" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I91" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Record_PartPayments_UpdateInvoicePaidPendingAndStatus; PaymentServiceTests.GetInvoicesWithPending_LeavesOutPaidInvoices</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
@@ -4373,12 +5266,22 @@
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H92" s="10" t="inlineStr"/>
-      <c r="I92" s="11" t="inlineStr"/>
-      <c r="J92" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Record_MoreThanPending_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -4413,12 +5316,22 @@
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H93" s="10" t="inlineStr"/>
-      <c r="I93" s="11" t="inlineStr"/>
-      <c r="J93" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I93" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Record_NonCashWithoutReference_IsRejected; PaymentServiceTests.Record_CashWithoutReference_IsAllowed</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
@@ -4453,12 +5366,22 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr"/>
-      <c r="I94" s="11" t="inlineStr"/>
-      <c r="J94" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Record_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -4493,12 +5416,22 @@
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H95" s="10" t="inlineStr"/>
-      <c r="I95" s="11" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Record_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
@@ -4533,12 +5466,22 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H96" s="10" t="inlineStr"/>
-      <c r="I96" s="11" t="inlineStr"/>
-      <c r="J96" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Receipt_IsWrittenToTheReceiptsFolderWithTheBalanceAfterThePayment; PaymentServiceTests.AmountInWords_UsesTheIndianSystem</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -4573,12 +5516,22 @@
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr"/>
-      <c r="I97" s="11" t="inlineStr"/>
-      <c r="J97" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I97" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.Delete_MakesTheAmountPendingAgain_AndInvoiceCanThenBeDeleted</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
@@ -4613,12 +5566,22 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H98" s="10" t="inlineStr"/>
-      <c r="I98" s="11" t="inlineStr"/>
-      <c r="J98" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Search box and filters on the Payments screen. Passed: PaymentServiceTests.GetPayments_ShowsOnlyTheHostelsPayments_NewestFirst</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
@@ -4653,12 +5616,22 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H99" s="10" t="inlineStr"/>
-      <c r="I99" s="11" t="inlineStr"/>
-      <c r="J99" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I99" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PendingDuesServiceTests.GetDues_GroupsUnpaidInvoicesPerStudent_MostOverdueFirst; PendingDuesServiceTests.View_ShowsOneRowPerStudentAndTheirInvoices</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -4693,12 +5666,22 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H100" s="10" t="inlineStr"/>
-      <c r="I100" s="11" t="inlineStr"/>
-      <c r="J100" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PendingDuesServiceTests.GetDues_GroupsUnpaidInvoicesPerStudent_MostOverdueFirst; PendingDuesServiceTests.GetDues_InvoiceNotYetDue_IsPendingButNotOverdue</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
@@ -4733,12 +5716,22 @@
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H101" s="10" t="inlineStr"/>
-      <c r="I101" s="11" t="inlineStr"/>
-      <c r="J101" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I101" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PendingDuesServiceTests.GetDues_IncludesStudentsWhoHaveLeft</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
@@ -4773,12 +5766,22 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H102" s="10" t="inlineStr"/>
-      <c r="I102" s="11" t="inlineStr"/>
-      <c r="J102" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PaymentServiceTests.PaymentForm_SuggestsThePendingAmountOfTheChosenInvoice; PaymentServiceTests.Record_PartPayments_UpdateInvoicePaidPendingAndStatus</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
@@ -4813,12 +5816,22 @@
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="inlineStr"/>
-      <c r="I103" s="11" t="inlineStr"/>
-      <c r="J103" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I103" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Real delivery through Gmail. Passed: EmailServiceTests.Reminders_GoOnlyToStudentsWithOverdueInvoices_AndListOnlyThoseInvoices; EmailServiceTests.Reminder_StudentWithNothingOverdue_IsRejected</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
@@ -4853,12 +5866,22 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H104" s="10" t="inlineStr"/>
-      <c r="I104" s="11" t="inlineStr"/>
-      <c r="J104" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I104" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Real delivery through Gmail. Passed: EmailServiceTests.Reminders_GoOnlyToStudentsWithOverdueInvoices_AndListOnlyThoseInvoices</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
@@ -4893,12 +5916,22 @@
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H105" s="10" t="inlineStr"/>
-      <c r="I105" s="11" t="inlineStr"/>
-      <c r="J105" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I105" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J105" s="10" t="inlineStr">
+        <is>
+          <t>Passed: PendingDuesServiceTests.Pdf_LongListContinuesOnFurtherPages; PendingDuesServiceTests.Pdf_WithoutDues_IsStillWritten; PendingDuesServiceTests.Pdf_FileNameIsSafe</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -4933,12 +5966,22 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H106" s="10" t="inlineStr"/>
-      <c r="I106" s="11" t="inlineStr"/>
-      <c r="J106" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Needs the Gmail app password, entered on the client PC. Passed: EmailServiceTests.TestEmail_GoesToTheChosenAddress_OrToTheSender</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
@@ -4976,9 +6019,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr"/>
-      <c r="I107" s="11" t="inlineStr"/>
-      <c r="J107" s="10" t="inlineStr"/>
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="11" t="n"/>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Needs the real Gmail account</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -5013,12 +6060,22 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H108" s="10" t="inlineStr"/>
-      <c r="I108" s="11" t="inlineStr"/>
-      <c r="J108" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I108" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J108" s="10" t="inlineStr">
+        <is>
+          <t>Passed: EmailServiceTests.InvalidSmtpServer_GivesAConnectionMessage</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -5053,12 +6110,22 @@
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr"/>
-      <c r="I109" s="11" t="inlineStr"/>
-      <c r="J109" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I109" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J109" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Real delivery through Gmail. Passed: EmailServiceTests.InvoiceEmail_GoesToTheParentWithThePdf_AndIsLogged; EmailServiceTests.EveryEmail_IsCopiedToTheAdmin</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -5093,12 +6160,22 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr"/>
-      <c r="I110" s="11" t="inlineStr"/>
-      <c r="J110" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J110" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Real delivery through Gmail. Passed: EmailServiceTests.ReceiptEmail_ShowsThePaymentAndBalance; EmailServiceTests.EveryEmail_IsCopiedToTheAdmin</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -5133,12 +6210,22 @@
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr"/>
-      <c r="I111" s="11" t="inlineStr"/>
-      <c r="J111" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I111" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J111" s="10" t="inlineStr">
+        <is>
+          <t>Passed: EmailServiceTests.Settings_EditedTextsAreKept</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
@@ -5173,12 +6260,22 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H112" s="10" t="inlineStr"/>
-      <c r="I112" s="11" t="inlineStr"/>
-      <c r="J112" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J112" s="10" t="inlineStr">
+        <is>
+          <t>Passed: EmailServiceTests.Settings_Rules; EmailServiceTests.Fill_ReplacesKnownFieldsAndLeavesOthers</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
@@ -5213,12 +6310,22 @@
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H113" s="10" t="inlineStr"/>
-      <c r="I113" s="11" t="inlineStr"/>
-      <c r="J113" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I113" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>Passed: EmailServiceTests.InvoiceEmail_GoesToTheParentWithThePdf_AndIsLogged; EmailServiceTests.FailedEmail_IsLoggedWithAMessageTheAdminCanActOn</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
@@ -5253,12 +6360,22 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H114" s="10" t="inlineStr"/>
-      <c r="I114" s="11" t="inlineStr"/>
-      <c r="J114" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I114" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J114" s="10" t="inlineStr">
+        <is>
+          <t>Passed: EmailServiceTests.PrepareInvoice_WithoutGmailAccount_AsksToSetItUp</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -5293,12 +6410,22 @@
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr"/>
-      <c r="I115" s="11" t="inlineStr"/>
-      <c r="J115" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I115" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DashboardServiceTests.Get_CountsStudentsBedsInvoicesPaymentsAndDues; DashboardServiceTests.Get_EmptyHostel_ShowsZerosAndTwelveMonthsFromJuly</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
@@ -5333,12 +6460,22 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr"/>
-      <c r="I116" s="11" t="inlineStr"/>
-      <c r="J116" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I116" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J116" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Hover over a bar to see the amount. Passed: DashboardServiceTests.View_ShowsTilesAndLabelsTheCurrentMonth</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
@@ -5373,12 +6510,22 @@
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr"/>
-      <c r="I117" s="11" t="inlineStr"/>
-      <c r="J117" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I117" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DashboardServiceTests.Get_ListsAtMostFiveOfEach</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
@@ -5413,12 +6560,22 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H118" s="10" t="inlineStr"/>
-      <c r="I118" s="11" t="inlineStr"/>
-      <c r="J118" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I118" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DashboardServiceTests.Get_CountsStudentsBedsInvoicesPaymentsAndDues; MainFormTests.MainForm_ShowsSelectedHostelAndFollowsChanges</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
@@ -5453,12 +6610,22 @@
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H119" s="10" t="inlineStr"/>
-      <c r="I119" s="11" t="inlineStr"/>
-      <c r="J119" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I119" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ReportServiceTests.StudentList_FiltersByStatusAndCollege_AndMasksAadhaar</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
@@ -5493,12 +6660,22 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H120" s="10" t="inlineStr"/>
-      <c r="I120" s="11" t="inlineStr"/>
-      <c r="J120" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ReportServiceTests.RoomOccupancy_ListsStudentsAndTotals</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
@@ -5533,12 +6710,22 @@
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr"/>
-      <c r="I121" s="11" t="inlineStr"/>
-      <c r="J121" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I121" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ReportServiceTests.PaymentsReceived_HasDailyAndMethodTotals_WithinTheDates</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
@@ -5573,12 +6760,22 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H122" s="10" t="inlineStr"/>
-      <c r="I122" s="11" t="inlineStr"/>
-      <c r="J122" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I122" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ReportServiceTests.Invoices_FilterByDateAndStatus_WithTotals</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
@@ -5613,12 +6810,22 @@
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H123" s="10" t="inlineStr"/>
-      <c r="I123" s="11" t="inlineStr"/>
-      <c r="J123" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I123" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ReportServiceTests.Pdf_LongReportHasSeveralPages</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
@@ -5653,12 +6860,22 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H124" s="10" t="inlineStr"/>
-      <c r="I124" s="11" t="inlineStr"/>
-      <c r="J124" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I124" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Open the file once in Excel. Passed: ReportServiceTests.Excel_HasRealNumbersDatesAndBoldTotals</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
@@ -5693,12 +6910,22 @@
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H125" s="10" t="inlineStr"/>
-      <c r="I125" s="11" t="inlineStr"/>
-      <c r="J125" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I125" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>Passed: ReportServiceTests.PaymentsReceived_HasDailyAndMethodTotals_WithinTheDates</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
@@ -5733,12 +6960,22 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr"/>
-      <c r="I126" s="11" t="inlineStr"/>
-      <c r="J126" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>Passed: BackupServiceTests.Create_ZipsTheDatabasePhotosAndDocuments; BackupServiceTests.Create_SameSecondTwice_KeepsBothFiles</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
@@ -5773,12 +7010,22 @@
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H127" s="10" t="inlineStr"/>
-      <c r="I127" s="11" t="inlineStr"/>
-      <c r="J127" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I127" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>Passed: BackupServiceTests.AutomaticBackup_IsMadeOnceADay; BackupServiceTests.OnlyTheLast30AutomaticBackupsAreKept_ManualOnesAreNeverDeleted</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
@@ -5813,12 +7060,22 @@
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H128" s="10" t="inlineStr"/>
-      <c r="I128" s="11" t="inlineStr"/>
-      <c r="J128" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I128" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>Passed: BackupServiceTests.SecondFolder_GetsACopy_AndAProblemIsReportedWhenItIsMissing; BackupServiceTests.SecondFolder_Rules</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
@@ -5853,12 +7110,22 @@
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H129" s="10" t="inlineStr"/>
-      <c r="I129" s="11" t="inlineStr"/>
-      <c r="J129" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I129" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>Passed: BackupServiceTests.SecondFolder_GetsACopy_AndAProblemIsReportedWhenItIsMissing</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
@@ -5893,12 +7160,22 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H130" s="10" t="inlineStr"/>
-      <c r="I130" s="11" t="inlineStr"/>
-      <c r="J130" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I130" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Program restart after restore. Passed: BackupServiceTests.Restore_ReplacesDataAndFiles_AfterSavingTheCurrentData; BackupServiceTests.Inspect_ReadsTheBackupDetails</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
@@ -5933,12 +7210,22 @@
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H131" s="10" t="inlineStr"/>
-      <c r="I131" s="11" t="inlineStr"/>
-      <c r="J131" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I131" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>Logic passed in the automated tests. Still check by hand: Restore the 'Before a restore' backup once. Passed: BackupServiceTests.Restore_ReplacesDataAndFiles_AfterSavingTheCurrentData</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
@@ -5973,12 +7260,22 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H132" s="10" t="inlineStr"/>
-      <c r="I132" s="11" t="inlineStr"/>
-      <c r="J132" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I132" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J132" s="10" t="inlineStr">
+        <is>
+          <t>Passed: BackupServiceTests.Inspect_RejectsFilesThatAreNotBackups; BackupServiceTests.Inspect_RejectsABackupFromAnOlderVersion</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
@@ -6013,12 +7310,22 @@
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr"/>
-      <c r="I133" s="11" t="inlineStr"/>
-      <c r="J133" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I133" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DatabaseCheckServiceTests.Run_AllStepsPass; DatabaseCheckServiceTests.Run_LeavesNoTestData</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
@@ -6056,9 +7363,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H134" s="10" t="inlineStr"/>
-      <c r="I134" s="11" t="inlineStr"/>
-      <c r="J134" s="10" t="inlineStr"/>
+      <c r="H134" s="10" t="n"/>
+      <c r="I134" s="11" t="n"/>
+      <c r="J134" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Click User Guide in Application Settings</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
@@ -6093,12 +7404,22 @@
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H135" s="10" t="inlineStr"/>
-      <c r="I135" s="11" t="inlineStr"/>
-      <c r="J135" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I135" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>Passed: MainFormTests.Menu_FitsWithoutScrollBarOnA768PixelScreen; MainFormTests.MenuPhoto_IsHiddenWhenThereIsNoSpareSpace</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
@@ -6133,12 +7454,22 @@
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="H136" s="10" t="inlineStr"/>
-      <c r="I136" s="11" t="inlineStr"/>
-      <c r="J136" s="10" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>Automated tests</t>
+        </is>
+      </c>
+      <c r="I136" s="17" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>Passed: DbTests.OpenConnection_MissingDatabaseFile_ThrowsFriendlyDatabaseException; DatabaseInitializerTests.Initialize_DatabaseFromBeforeVersioning_IsRejectedWithFriendlyMessage; EmailServiceTests.FailedEmail_IsLoggedWithAMessageTheAdminCanActOn</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
@@ -6176,9 +7507,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H137" s="10" t="inlineStr"/>
-      <c r="I137" s="11" t="inlineStr"/>
-      <c r="J137" s="10" t="inlineStr"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="11" t="n"/>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Uninstall on the client PC</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
@@ -6216,9 +7551,13 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="H138" s="10" t="inlineStr"/>
-      <c r="I138" s="11" t="inlineStr"/>
-      <c r="J138" s="10" t="inlineStr"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="11" t="n"/>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>Manual check on the client PC: Reinstall on the client PC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J138"/>
@@ -6256,7 +7595,7 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6315,7 +7654,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-001 to TC-004</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -6341,7 +7684,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-008</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
@@ -6367,7 +7714,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-013, TC-015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -6393,7 +7744,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-105</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -6419,7 +7774,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -6445,7 +7804,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -6471,7 +7834,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-027</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -6497,7 +7864,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-029</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -6523,7 +7894,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-036</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -6549,7 +7924,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-039, TC-044, TC-046</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -6575,7 +7954,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-053</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -6601,7 +7984,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-061, TC-062</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -6627,7 +8014,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-070, TC-076</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -6653,7 +8044,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-078</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -6679,7 +8074,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-108</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -6705,7 +8104,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-089</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -6731,7 +8134,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-109</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -6757,7 +8164,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-098, TC-099</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -6783,7 +8194,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-090</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -6809,7 +8224,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-114</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -6835,7 +8254,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-120, TC-122, TC-123</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -6861,7 +8284,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-059</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -6887,7 +8314,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-125</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -6913,7 +8344,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-129</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -6939,7 +8374,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-060</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
@@ -6965,7 +8404,11 @@
           <t>Not run</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>To run on the client PC. Related test cases: TC-136, TC-137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E27">
@@ -7796,4 +9239,762 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Automated test run</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>08-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>9512db4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Actions, Windows Server (windows-latest) with Microsoft Access Database Engine 2016 x64</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Three full runs of the same build (58, 59, 60): 319 of 319 passed in each</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Run 58</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/offbeatsoftware/hostelmanagement/actions/runs/37736840117</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Run 59</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/offbeatsoftware/hostelmanagement/actions/runs/37736847211</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Run 60</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/offbeatsoftware/hostelmanagement/actions/runs/37736850027</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Test class</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>AgreementServiceTests</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Agreement and beds</t>
+        </is>
+      </c>
+      <c r="C13" s="20">
+        <f>D13+E13</f>
+        <v/>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>AllocationServiceTests</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Room Allocation</t>
+        </is>
+      </c>
+      <c r="C14" s="20">
+        <f>D14+E14</f>
+        <v/>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>AttendanceServiceTests</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="C15" s="20">
+        <f>D15+E15</f>
+        <v/>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>AuthServiceTests</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Sign in and Admin Account</t>
+        </is>
+      </c>
+      <c r="C16" s="20">
+        <f>D16+E16</f>
+        <v/>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>BackupServiceTests</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Backup / Restore</t>
+        </is>
+      </c>
+      <c r="C17" s="20">
+        <f>D17+E17</f>
+        <v/>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>BillingPeriodsTests</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Billing periods</t>
+        </is>
+      </c>
+      <c r="C18" s="20">
+        <f>D18+E18</f>
+        <v/>
+      </c>
+      <c r="D18" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>CollegeServiceTests</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Colleges</t>
+        </is>
+      </c>
+      <c r="C19" s="20">
+        <f>D19+E19</f>
+        <v/>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>DashboardServiceTests</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C20" s="20">
+        <f>D20+E20</f>
+        <v/>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>DatabaseCheckServiceTests</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Application Settings</t>
+        </is>
+      </c>
+      <c r="C21" s="20">
+        <f>D21+E21</f>
+        <v/>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>DatabaseInitializerTests</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Database setup</t>
+        </is>
+      </c>
+      <c r="C22" s="20">
+        <f>D22+E22</f>
+        <v/>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>DatabaseTemplateExport</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Empty database for the installer</t>
+        </is>
+      </c>
+      <c r="C23" s="20">
+        <f>D23+E23</f>
+        <v/>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>DbTests</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Data access</t>
+        </is>
+      </c>
+      <c r="C24" s="20">
+        <f>D24+E24</f>
+        <v/>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>EmailServiceTests</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C25" s="20">
+        <f>D25+E25</f>
+        <v/>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>HostelServiceTests</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Hostels</t>
+        </is>
+      </c>
+      <c r="C26" s="20">
+        <f>D26+E26</f>
+        <v/>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>InvoiceServiceTests</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="C27" s="20">
+        <f>D27+E27</f>
+        <v/>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>MainFormTests</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Main window and menu</t>
+        </is>
+      </c>
+      <c r="C28" s="20">
+        <f>D28+E28</f>
+        <v/>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>MoneyAndSortingTests</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Amounts and sorting</t>
+        </is>
+      </c>
+      <c r="C29" s="20">
+        <f>D29+E29</f>
+        <v/>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>ParentServiceTests</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Parents</t>
+        </is>
+      </c>
+      <c r="C30" s="20">
+        <f>D30+E30</f>
+        <v/>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>PaymentServiceTests</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="C31" s="20">
+        <f>D31+E31</f>
+        <v/>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>PendingDuesServiceTests</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>Pending Dues</t>
+        </is>
+      </c>
+      <c r="C32" s="20">
+        <f>D32+E32</f>
+        <v/>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>ReportServiceTests</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C33" s="20">
+        <f>D33+E33</f>
+        <v/>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>RoomServiceTests</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C34" s="20">
+        <f>D34+E34</f>
+        <v/>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>ScreenshotTests</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Screens (images)</t>
+        </is>
+      </c>
+      <c r="C35" s="20">
+        <f>D35+E35</f>
+        <v/>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>ServiceItemServiceTests</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C36" s="20">
+        <f>D36+E36</f>
+        <v/>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>StudentServiceTests</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C37" s="20">
+        <f>D37+E37</f>
+        <v/>
+      </c>
+      <c r="D37" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>ValidatorsTests</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Input checks</t>
+        </is>
+      </c>
+      <c r="C38" s="20">
+        <f>D38+E38</f>
+        <v/>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="21">
+        <f>SUM(C13:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="21">
+        <f>SUM(D13:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="21">
+        <f>SUM(E13:E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>A theory test runs once per data row, so the 319 runs come from 249 test methods. Each test uses its own new database.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/TestCases.xlsx
+++ b/docs/TestCases.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$J$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$J$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1028,27 +1028,27 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Sign in</t>
+          <t>Installation</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Default user name filled in</t>
+          <t>Update from version 1.2 keeps data</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Start the program</t>
+          <t>Install 1.2.1 over 1.2 with students and payments</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>User name shows admin; cursor is in the password box</t>
+          <t>Database upgraded in place; all data kept</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -1073,22 +1073,22 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Correct login</t>
+          <t>Default user name filled in</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Password admin &gt; Sign in</t>
+          <t>Start the program</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Main window opens on the Dashboard</t>
+          <t>User name shows admin; cursor is in the password box</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Wrong password</t>
+          <t>Correct login</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Enter a wrong password &gt; Sign in</t>
+          <t>Password admin &gt; Sign in</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Message 'Incorrect user name or password'; password box cleared</t>
+          <t>Main window opens on the Dashboard</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -1153,22 +1153,22 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>User name not case sensitive</t>
+          <t>Wrong password</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>User name ADMIN, correct password</t>
+          <t>Enter a wrong password &gt; Sign in</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Sign in succeeds</t>
+          <t>Message 'Incorrect user name or password'; password box cleared</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Password is case sensitive</t>
+          <t>User name not case sensitive</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Password ADMIN</t>
+          <t>User name ADMIN, correct password</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Sign in refused</t>
+          <t>Sign in succeeds</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -1233,17 +1233,17 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Hostel chosen at sign in</t>
+          <t>Password is case sensitive</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>With two hostels, choose the second at sign in</t>
+          <t>Password ADMIN</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Main window shows the second hostel at the top right</t>
+          <t>Sign in refused</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -1268,27 +1268,27 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Admin Account</t>
+          <t>Sign in</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Save admin email and phone</t>
+          <t>Hostel chosen at sign in</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Settings &gt; Admin Account &gt; enter email and phone &gt; Save</t>
+          <t>With two hostels, choose the second at sign in</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>'Saved.' shown; values kept after restarting</t>
+          <t>Main window shows the second hostel at the top right</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Invalid email</t>
+          <t>Save admin email and phone</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Enter 'owner' as email &gt; Save</t>
+          <t>Settings &gt; Admin Account &gt; enter email and phone &gt; Save</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Error 'Please enter a valid email address'</t>
+          <t>'Saved.' shown; values kept after restarting</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Invalid email</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Current admin, new Balaji@2026 twice &gt; Change Password</t>
+          <t>Enter 'owner' as email &gt; Save</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Success message; next sign in works only with the new password</t>
+          <t>Error 'Please enter a valid email address'</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Wrong current password</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Wrong current password &gt; Change Password</t>
+          <t>Current admin, new Balaji@2026 twice &gt; Change Password</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Error 'The current password is not correct'</t>
+          <t>Success message; next sign in works only with the new password</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1433,22 +1433,22 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Password too short</t>
+          <t>Wrong current password</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>New password abc</t>
+          <t>Wrong current password &gt; Change Password</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Error 'at least 6 characters'</t>
+          <t>Error 'The current password is not correct'</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Confirmation differs</t>
+          <t>Password too short</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>New and confirm different</t>
+          <t>New password abc</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Error 'not the same'</t>
+          <t>Error 'at least 6 characters'</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -1508,27 +1508,27 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Hostels</t>
+          <t>Admin Account</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Add hostel</t>
+          <t>Confirmation differs</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Hostels &gt; Add &gt; name, address, phone &gt; Save</t>
+          <t>New and confirm different</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Hostel listed; appears in the hostel selector</t>
+          <t>Error 'not the same'</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1553,22 +1553,22 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Name required</t>
+          <t>Add hostel</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Add without a name</t>
+          <t>Hostels &gt; Add &gt; name, address, phone &gt; Save</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Error, nothing saved</t>
+          <t>Hostel listed; appears in the hostel selector</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1593,17 +1593,17 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Duplicate hostel name</t>
+          <t>Name required</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Add a hostel with an existing name</t>
+          <t>Add without a name</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Error about the duplicate name</t>
+          <t>Error, nothing saved</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Default sharing types</t>
+          <t>Duplicate hostel name</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Open Rooms &gt; Add for the new hostel</t>
+          <t>Add a hostel with an existing name</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Single (1 bed), Double (2 beds), Triple (3 beds) offered; no rent asked</t>
+          <t>Error about the duplicate name</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -1673,22 +1673,22 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Switch hostel</t>
+          <t>Default sharing types</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Choose another hostel at the top right</t>
+          <t>Open Rooms &gt; Add for the new hostel</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Every screen shows only that hostel's data</t>
+          <t>Single (1 bed), Double (2 beds), Triple (3 beds) offered; no rent asked</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Colleges</t>
+          <t>Hostels</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Add college</t>
+          <t>Switch hostel</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Colleges &gt; Add &gt; name &gt; Save</t>
+          <t>Choose another hostel at the top right</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>College listed for the selected hostel only</t>
+          <t>Every screen shows only that hostel's data</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -1753,22 +1753,22 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Duplicate college in same hostel</t>
+          <t>Add college</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Add the same college name again</t>
+          <t>Colleges &gt; Add &gt; name &gt; Save</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Error about the duplicate</t>
+          <t>College listed for the selected hostel only</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -1793,22 +1793,22 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Delete college in use</t>
+          <t>Duplicate college in same hostel</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Delete a college that has students</t>
+          <t>Add the same college name again</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Refused with a clear message</t>
+          <t>Error about the duplicate</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -1828,27 +1828,27 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Colleges</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>No rent on rooms</t>
+          <t>Delete college in use</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Open Rooms</t>
+          <t>Delete a college that has students</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>No rent panel or rent column; sharing type only sets the number of beds</t>
+          <t>Refused with a clear message</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -1873,17 +1873,17 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Add room</t>
+          <t>No rent on rooms</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Add room 101, Double, Boys</t>
+          <t>Open Rooms</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Room listed with 2 beds, 0 occupied, 2 free</t>
+          <t>No rent panel or rent column; sharing type only sets the number of beds</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Duplicate room number</t>
+          <t>Add room</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Add room 101 again (any case)</t>
+          <t>Add room 101, Double, Boys</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Error about the duplicate</t>
+          <t>Room listed with 2 beds, 0 occupied, 2 free</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -1953,22 +1953,22 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Room for boys or girls required</t>
+          <t>Duplicate room number</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Add a room without choosing Boys/Girls</t>
+          <t>Add room 101 again (any case)</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Error about the duplicate</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Reduce sharing below occupancy</t>
+          <t>Room for boys or girls required</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Room with 2 students &gt; change to Single</t>
+          <t>Add a room without choosing Boys/Girls</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Change gender of occupied room</t>
+          <t>Reduce sharing below occupancy</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Occupied boys room &gt; change to Girls</t>
+          <t>Room with 2 students &gt; change to Single</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Deactivate occupied room</t>
+          <t>Change gender of occupied room</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Occupied room &gt; untick Active</t>
+          <t>Occupied boys room &gt; change to Girls</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Delete room</t>
+          <t>Deactivate occupied room</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Delete a room never used / a room with past students</t>
+          <t>Occupied room &gt; untick Active</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Unused room deleted; used room refused</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -2148,27 +2148,27 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Add student with required fields</t>
+          <t>Delete room</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Students &gt; Add &gt; name, gender, mobile, college, admission date, father's name and mobile &gt; Save</t>
+          <t>Delete a room never used / a room with past students</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Student listed as Active</t>
+          <t>Unused room deleted; used room refused</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Required fields</t>
+          <t>Add student with required fields</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Save without name / mobile / admission date / father's name / father's mobile</t>
+          <t>Students &gt; Add &gt; name, gender, mobile, college, admission date, father's name and mobile &gt; Save</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Clear error for each missing field; nothing saved</t>
+          <t>Student listed as Active</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -2233,22 +2233,22 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Invalid mobile or email</t>
+          <t>Required fields</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Mobile 12ab, father's email 'abc', mother's mobile 12ab</t>
+          <t>Save without name / mobile / admission date / father's name / father's mobile</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Errors shown</t>
+          <t>Clear error for each missing field; nothing saved</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Aadhaar check</t>
+          <t>Invalid mobile or email</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Enter 2345 6789 0124 (valid) and 2345 6789 0123 (invalid)</t>
+          <t>Mobile 12ab, father's email 'abc', mother's mobile 12ab</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Valid one saved; invalid one refused</t>
+          <t>Errors shown</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2313,22 +2313,22 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Aadhaar masked</t>
+          <t>Aadhaar check</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>View student list and reports</t>
+          <t>Enter 2345 6789 0124 (valid) and 2345 6789 0123 (invalid)</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Aadhaar shown as XXXX XXXX 0124 only</t>
+          <t>Valid one saved; invalid one refused</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -2353,22 +2353,22 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Photo and Aadhaar card</t>
+          <t>Aadhaar masked</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Add a JPG photo and a PDF Aadhaar card</t>
+          <t>View student list and reports</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Photo shown; files saved in Photos/Documents</t>
+          <t>Aadhaar shown as XXXX XXXX 0124 only</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -2393,22 +2393,22 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>File too large or wrong type</t>
+          <t>Photo and Aadhaar card</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Add a 6 MB photo or a .txt file</t>
+          <t>Add a JPG photo and a PDF Aadhaar card</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Refused before saving</t>
+          <t>Photo shown; files saved in Photos/Documents</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -2433,22 +2433,22 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Search and filters</t>
+          <t>File too large or wrong type</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Type part of a student, father or mother name or mobile; filter by college, course, class, status</t>
+          <t>Add a 6 MB photo or a .txt file</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>List narrows correctly</t>
+          <t>Refused before saving</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -2473,17 +2473,17 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Edit student</t>
+          <t>Search and filters</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>View / Edit &gt; change mobile &gt; Save</t>
+          <t>Type part of a student, father or mother name or mobile; filter by college, course, class, status</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Change saved</t>
+          <t>List narrows correctly</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Delete student with history</t>
+          <t>Edit student</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Delete a student who had a room or invoice</t>
+          <t>View / Edit &gt; change mobile &gt; Save</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Change saved</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -2553,22 +2553,22 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Father and mother details</t>
+          <t>Delete student with history</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Father &amp; Mother tab: father name, mobile, email; mother name, mobile, email &gt; Save</t>
+          <t>Delete a student who had a room or invoice</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>All six values kept; Father and Father mobile shown in the list</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -2593,22 +2593,22 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Only father details</t>
+          <t>Father and mother details</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Leave father email and all mother fields empty &gt; Save</t>
+          <t>Father &amp; Mother tab: father name, mobile, email; mother name, mobile, email &gt; Save</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Saved (only father name and mobile are required)</t>
+          <t>All six values kept; Father and Father mobile shown in the list</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -2633,22 +2633,22 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Take photo with webcam</t>
+          <t>Only father details</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Photo &amp; Aadhaar &gt; Take Photo &gt; Capture &gt; Use Photo &gt; Save</t>
+          <t>Leave father email and all mother fields empty &gt; Save</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Live picture shown; captured photo saved with the student</t>
+          <t>Saved (only father name and mobile are required)</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -2673,22 +2673,22 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Retake photo</t>
+          <t>Take photo with webcam</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Take Photo &gt; Capture &gt; Retake &gt; Capture &gt; Use Photo</t>
+          <t>Photo &amp; Aadhaar &gt; Take Photo &gt; Capture &gt; Use Photo &gt; Save</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>The second picture is used</t>
+          <t>Live picture shown; captured photo saved with the student</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -2713,22 +2713,22 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>No camera / camera blocked</t>
+          <t>Retake photo</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Take Photo on a PC without camera, or with camera access off in Windows</t>
+          <t>Take Photo &gt; Capture &gt; Retake &gt; Capture &gt; Use Photo</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Clear message (connect a camera / switch on camera access); Choose Photo still works</t>
+          <t>The second picture is used</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -2753,22 +2753,22 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Student I-card</t>
+          <t>No camera / camera blocked</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Select a student &gt; I-Card &gt; Save</t>
+          <t>Take Photo on a PC without camera, or with camera access off in Windows</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>PDF opens: card with photo, name, father, college, room and bed, mobiles, valid till 30 Jun</t>
+          <t>Clear message (connect a camera / switch on camera access); Choose Photo still works</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -2793,22 +2793,22 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>I-cards for several students</t>
+          <t>Student I-card</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Select 9 students (Ctrl/Shift) &gt; I-Card</t>
+          <t>Select a student &gt; I-Card &gt; Save</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>8 cards on page 1, 1 on page 2</t>
+          <t>PDF opens: card with photo, name, father, college, room and bed, mobiles, valid till 30 Jun</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -2833,22 +2833,22 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Transport I-card</t>
+          <t>I-cards for several students</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Select a student with transport and one without &gt; Transport I-Card</t>
+          <t>Select 9 students (Ctrl/Shift) &gt; I-Card</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Transport pass only for the student with transport; message names the other</t>
+          <t>8 cards on page 1, 1 on page 2</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>I-card without photo</t>
+          <t>Transport I-card</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>I-Card for a student without photo</t>
+          <t>Select a student with transport and one without &gt; Transport I-Card</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Card with empty photo box; message names the student</t>
+          <t>Transport pass only for the student with transport; message names the other</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>I-card for student who left</t>
+          <t>I-card without photo</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>I-Card for a student with status Left</t>
+          <t>I-Card for a student without photo</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>No card; message 'has left the hostel'</t>
+          <t>Card with empty photo box; message names the student</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -2948,27 +2948,27 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Room Allocation</t>
+          <t>Students</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Check-in with yearly fee</t>
+          <t>I-card for student who left</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Room Allocation &gt; Check-in &gt; student, room 101 &gt; rent 50000, transport 12000 &gt; Check-in</t>
+          <t>I-Card for a student with status Left</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Bed 1 suggested; student in room 101 bed 1; total 62000 shown; invoice for this academic year created</t>
+          <t>No card; message 'has left the hostel'</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -2993,22 +2993,22 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Choose another bed</t>
+          <t>Check-in with yearly fee</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Check-in a second student, choose bed 2</t>
+          <t>Room Allocation &gt; Check-in &gt; student, room 101 &gt; rent 50000, transport 12000 &gt; Check-in</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Saved in bed 2</t>
+          <t>Bed 1 suggested; student in room 101 bed 1; total 62000 shown; invoice for this academic year created</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Only matching rooms offered</t>
+          <t>Choose another bed</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Check in a girl student</t>
+          <t>Check-in a second student, choose bed 2</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Only girls' rooms with a free bed listed</t>
+          <t>Saved in bed 2</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Full room</t>
+          <t>Only matching rooms offered</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Try to fill a room beyond its beds</t>
+          <t>Check in a girl student</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Full room not offered / refused</t>
+          <t>Only girls' rooms with a free bed listed</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -3113,22 +3113,22 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Check-in before admission date</t>
+          <t>Full room</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Check-in date earlier than admission date</t>
+          <t>Try to fill a room beyond its beds</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Full room not offered / refused</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
@@ -3153,17 +3153,17 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Future date</t>
+          <t>Check-in before admission date</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Check-in date in the future</t>
+          <t>Check-in date earlier than admission date</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Not possible</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
@@ -3193,22 +3193,22 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Future date</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Transfer &gt; new room and bed &gt; confirm</t>
+          <t>Check-in date in the future</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Old stay closed as Transferred, new stay current, same day</t>
+          <t>Not possible</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Check-out</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Check-out &gt; confirm</t>
+          <t>Transfer &gt; new room and bed &gt; confirm</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Stay closed; student status Left; bed free</t>
+          <t>Old stay closed as Transferred, new stay current, same day</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
@@ -3273,22 +3273,22 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Agreement offered after check-in</t>
+          <t>Check-out</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Complete a check-in</t>
+          <t>Check-out &gt; confirm</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Program offers to create the agreement PDF</t>
+          <t>Stay closed; student status Left; bed free</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -3313,22 +3313,22 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Rent required at check-in</t>
+          <t>Agreement offered after check-in</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Check-in with the rent empty or 0</t>
+          <t>Complete a check-in</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Refused: enter the room rent for the year; nothing saved</t>
+          <t>Program offers to create the agreement PDF</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Different fees in one room</t>
+          <t>Rent required at check-in</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Check in two students to the same Double room with rent 50000 and 45000</t>
+          <t>Check-in with the rent empty or 0</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Each student's invoice has his own amount</t>
+          <t>Refused: enter the room rent for the year; nothing saved</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
@@ -3393,22 +3393,22 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Student who already has a fee</t>
+          <t>Different fees in one room</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Check in again a student who already has this year's fee</t>
+          <t>Check in two students to the same Double room with rent 50000 and 45000</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Fee boxes locked showing the existing invoice; no second invoice</t>
+          <t>Each student's invoice has his own amount</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Transfer and check-out keep the fee</t>
+          <t>Student who already has a fee</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Transfer, then check out a student</t>
+          <t>Check in again a student who already has this year's fee</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Invoice amounts unchanged; pending still due</t>
+          <t>Fee boxes locked showing the existing invoice; no second invoice</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -3468,27 +3468,27 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Agreement</t>
+          <t>Room Allocation</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Create agreement PDF</t>
+          <t>Transfer and check-out keep the fee</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Students &gt; select &gt; Agreement PDF &gt; Save</t>
+          <t>Transfer, then check out a student</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>PDF opens: name, S/o or D/o + father, address, Boys/Girls hostel, room, bed, beds in room, check-in date, annual fee in figures and words</t>
+          <t>Invoice amounts unchanged; pending still due</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Annual fee with transport</t>
+          <t>Create agreement PDF</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Student with rent 120000 and transport 18000 at check-in</t>
+          <t>Students &gt; select &gt; Agreement PDF &gt; Save</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Annual fee Rs. 1,38,000/- (Rupees One Lakh Thirty Eight Thousand Only)</t>
+          <t>PDF opens: name, S/o or D/o + father, address, Boys/Girls hostel, room, bed, beds in room, check-in date, annual fee in figures and words</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Girl student</t>
+          <t>Annual fee with transport</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Agreement for a girl</t>
+          <t>Student with rent 120000 and transport 18000 at check-in</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>D/o and 'Girls Hostel'</t>
+          <t>Annual fee Rs. 1,38,000/- (Rupees One Lakh Thirty Eight Thousand Only)</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
@@ -3593,22 +3593,22 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>No address</t>
+          <t>Girl student</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Student without address</t>
+          <t>Agreement for a girl</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Dotted line after R/o</t>
+          <t>D/o and 'Girls Hostel'</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -3633,22 +3633,22 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Student not checked in</t>
+          <t>No address</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Agreement PDF for a student without a room</t>
+          <t>Student without address</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Message to check in first</t>
+          <t>Dotted line after R/o</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Edit agreement text</t>
+          <t>Student not checked in</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Students &gt; Agreement Text &gt; change a rule &gt; Save &gt; create PDF</t>
+          <t>Agreement PDF for a student without a room</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>PDF shows the changed text; Restore Default brings back the original</t>
+          <t>Message to check in first</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
@@ -3713,22 +3713,22 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Unknown field in text</t>
+          <t>Edit agreement text</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Type {BedNo} in the text &gt; Save</t>
+          <t>Students &gt; Agreement Text &gt; change a rule &gt; Save &gt; create PDF</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Error naming the available fields</t>
+          <t>PDF shows the changed text; Restore Default brings back the original</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -3748,27 +3748,27 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Attendance</t>
+          <t>Agreement</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tonight's sheet</t>
+          <t>Unknown field in text</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Students &gt; Attendance</t>
+          <t>Type {BedNo} in the text &gt; Save</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Today's date; all students in a room tonight with room and bed; all Present; 'Not marked yet'</t>
+          <t>Error naming the available fields</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -3793,17 +3793,17 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Mark absent and save</t>
+          <t>Tonight's sheet</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Untick Present for 2 students &gt; Save Attendance</t>
+          <t>Students &gt; Attendance</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>'Saved: x present, 2 absent'; both in the Absent students list</t>
+          <t>Today's date; all students in a room tonight with room and bed; all Present; 'Not marked yet'</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Earlier date</t>
+          <t>Mark absent and save</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Choose yesterday</t>
+          <t>Untick Present for 2 students &gt; Save Attendance</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Yesterday's saved attendance (or all present, not marked)</t>
+          <t>'Saved: x present, 2 absent'; both in the Absent students list</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
@@ -3873,22 +3873,22 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Correct an earlier date</t>
+          <t>Earlier date</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Change yesterday's attendance &gt; Save</t>
+          <t>Choose yesterday</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Correction saved</t>
+          <t>Yesterday's saved attendance (or all present, not marked)</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Future date</t>
+          <t>Correct an earlier date</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Try to choose tomorrow</t>
+          <t>Change yesterday's attendance &gt; Save</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Not possible</t>
+          <t>Correction saved</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -3953,22 +3953,22 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Unsaved changes</t>
+          <t>Future date</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Change ticks, then pick another date</t>
+          <t>Try to choose tomorrow</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Asks whether to discard the changes</t>
+          <t>Not possible</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -3993,17 +3993,17 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Checked out student</t>
+          <t>Unsaved changes</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Check out a student today</t>
+          <t>Change ticks, then pick another date</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Not on tonight's sheet; still on earlier nights</t>
+          <t>Asks whether to discard the changes</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
@@ -4033,22 +4033,22 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Email parents of absent</t>
+          <t>Checked out student</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Email Parents &gt; confirm</t>
+          <t>Check out a student today</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Email goes to the mother (father when no mother email); 'Emailed' shown; copy to admin; in Email history</t>
+          <t>Not on tonight's sheet; still on earlier nights</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -4073,22 +4073,22 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Email again</t>
+          <t>Email parents of absent</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Click Email Parents again for the same date</t>
+          <t>Email Parents &gt; confirm</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Asks before emailing the same parents again</t>
+          <t>Email goes to the mother (father when no mother email); 'Emailed' shown; copy to admin; in Email history</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
@@ -4113,22 +4113,22 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>No parent email</t>
+          <t>Email again</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Absent student without father or mother email &gt; Email Parents</t>
+          <t>Click Email Parents again for the same date</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Listed as a problem; others are emailed</t>
+          <t>Asks before emailing the same parents again</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -4148,27 +4148,27 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Attendance</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Invoice from check-in</t>
+          <t>No parent email</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Invoices after a check-in with rent 50000 + transport 12000</t>
+          <t>Absent student without father or mother email &gt; Email Parents</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Invoice SBH/2026-27/0001, year 2026-27, rent 50000, transport 12000, total 62000, Unpaid</t>
+          <t>Listed as a problem; others are emailed</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Joining mid-year</t>
+          <t>Invoice from check-in</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Check in a student in January</t>
+          <t>Invoices after a check-in with rent 50000 + transport 12000</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Full yearly fee charged</t>
+          <t>Invoice SBH/2026-27/0001, year 2026-27, rent 50000, transport 12000, total 62000, Unpaid</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Edit fee</t>
+          <t>Joining mid-year</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Select invoice &gt; Edit Fee &gt; transport 0 &gt; Save</t>
+          <t>Check in a student in January</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Total and pending updated</t>
+          <t>Full yearly fee charged</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -4273,17 +4273,17 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Edit fee below paid</t>
+          <t>Edit fee</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Paid 15000 &gt; Edit Fee total 10000</t>
+          <t>Select invoice &gt; Edit Fee &gt; transport 0 &gt; Save</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Refused: cannot be less than paid</t>
+          <t>Total and pending updated</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
@@ -4313,17 +4313,17 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>New Year Fees</t>
+          <t>Edit fee below paid</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>New Year Fees &gt; next year &gt; rent and transport for 2 students &gt; Create Fees</t>
+          <t>Paid 15000 &gt; Edit Fee total 10000</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>2 invoices SBH/next-year/0001, 0002; last year's amounts shown for reference</t>
+          <t>Refused: cannot be less than paid</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
@@ -4353,22 +4353,22 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>New Year Fees skips empty rows</t>
+          <t>New Year Fees</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Leave a student's row empty &gt; Create Fees</t>
+          <t>New Year Fees &gt; next year &gt; rent and transport for 2 students &gt; Create Fees</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>That student gets no fee; others created</t>
+          <t>2 invoices SBH/next-year/0001, 0002; last year's amounts shown for reference</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -4393,17 +4393,17 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>New Year Fees wrong amount</t>
+          <t>New Year Fees skips empty rows</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Rent 0 or letters for one student</t>
+          <t>Leave a student's row empty &gt; Create Fees</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Error naming the student; nothing created</t>
+          <t>That student gets no fee; others created</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Numbering</t>
+          <t>New Year Fees wrong amount</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Create three fees</t>
+          <t>Rent 0 or letters for one student</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>0001, 0002, 0003 in the academic year</t>
+          <t>Error naming the student; nothing created</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
@@ -4473,22 +4473,22 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>View / Print with payments</t>
+          <t>Numbering</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Invoice with two payments &gt; View / Print</t>
+          <t>Create three fees</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>PDF: room rent, transport, total, both payments (date, receipt, method), total paid, pending</t>
+          <t>0001, 0002, 0003 in the academic year</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -4513,22 +4513,22 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>View / Print with payments</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Status Partly paid; Year 2026-27; search a name</t>
+          <t>Invoice with two payments &gt; View / Print</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>List narrows; totals update</t>
+          <t>PDF: room rent, transport, total, both payments (date, receipt, method), total paid, pending</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -4553,22 +4553,22 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Delete invoice</t>
+          <t>Filters</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Delete an invoice without payments / with a payment</t>
+          <t>Status Partly paid; Year 2026-27; search a name</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Deleted / refused (use Edit Fee)</t>
+          <t>List narrows; totals update</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Part payment</t>
+          <t>Delete invoice</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Fee 62000 &gt; Record Payment 10000 Cash</t>
+          <t>Delete an invoice without payments / with a payment</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Receipt SBH/R/2026-27/0001; invoice Partly paid, pending 52000</t>
+          <t>Deleted / refused (use Edit Fee)</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -4633,17 +4633,17 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Further instalments</t>
+          <t>Part payment</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Pay 5000 after 15 days, then the remaining 47000 by UPI</t>
+          <t>Fee 62000 &gt; Record Payment 10000 Cash</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Pending 47000, then 0; invoice Paid; Record Payment disabled</t>
+          <t>Receipt SBH/R/2026-27/0001; invoice Partly paid, pending 52000</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
@@ -4673,17 +4673,17 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>More than pending</t>
+          <t>Further instalments</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Enter 60000 when 47000 is pending</t>
+          <t>Pay 5000 after 15 days, then the remaining 47000 by UPI</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Refused (no advance payments)</t>
+          <t>Pending 47000, then 0; invoice Paid; Record Payment disabled</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Reference required</t>
+          <t>More than pending</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Cheque / UPI / Bank transfer without reference</t>
+          <t>Enter 60000 when 47000 is pending</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Refused (no advance payments)</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Invalid amount</t>
+          <t>Reference required</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>0, negative, 100.555, letters</t>
+          <t>Cheque / UPI / Bank transfer without reference</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -4793,22 +4793,22 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Future date</t>
+          <t>Invalid amount</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Payment date tomorrow</t>
+          <t>0, negative, 100.555, letters</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Not possible</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
@@ -4833,22 +4833,22 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Receipt PDF</t>
+          <t>Future date</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Payments &gt; View / Print</t>
+          <t>Payment date tomorrow</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Receipt with amount in words and balance pending</t>
+          <t>Not possible</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Delete payment</t>
+          <t>Receipt PDF</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Delete a payment &gt; confirm</t>
+          <t>Payments &gt; View / Print</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>Amount pending again on the invoice</t>
+          <t>Receipt with amount in words and balance pending</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G105" s="10" t="inlineStr">
@@ -4948,22 +4948,22 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Fee Reminders</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Edit payment</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Fee Reminders</t>
+          <t>Payments &gt; select &gt; Edit &gt; amount 10000 to 12000, Cash to UPI with reference, reason &gt; Save</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>One row per student with pending fee: total, paid, pending, email goes to, last reminder; highest pending first</t>
+          <t>Same receipt number; amount and method corrected; pending reduced by 2000</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
@@ -4988,27 +4988,27 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Fee Reminders</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Left student</t>
+          <t>Edit above the fee</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Check out a student with pending fee</t>
+          <t>Edit a payment to more than the fee less the other payments</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Still listed as '(left)'</t>
+          <t>Refused with the maximum allowed amount</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Fee Reminders</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Tick and send</t>
+          <t>Edit without changes</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Tick 2 students &gt; Send Reminder (2) &gt; confirm</t>
+          <t>Edit &gt; Save without changing anything</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>2 emails with total, paid, pending and invoice PDF; copy to admin; Last reminder date shown</t>
+          <t>Message 'Nothing was changed'</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -5068,22 +5068,22 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Fee Reminders</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Father, else mother</t>
+          <t>Delete with reason</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Student without father email but with mother email</t>
+          <t>Payments &gt; Delete &gt; reason Entered twice &gt; Delete</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>Email to the mother; 'Mother: ...' shown</t>
+          <t>Payment removed; amount pending again</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
@@ -5108,27 +5108,27 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Fee Reminders</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>No parent email</t>
+          <t>Change history</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Tick a student with no father or mother email &gt; Send</t>
+          <t>Payments &gt; Change History</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Shown in red; listed as a problem; others sent</t>
+          <t>Every edit and delete with date, receipt, student, old and new values, reason; deletions in red</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
@@ -5153,22 +5153,22 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Select All / Clear</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Select All, then Clear</t>
+          <t>Fee Reminders</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>All emailable students ticked, then none; button count updates</t>
+          <t>One row per student with pending fee: total, paid, pending, email goes to, last reminder; highest pending first</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G112" s="10" t="inlineStr">
@@ -5193,22 +5193,22 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Preview</t>
+          <t>Left student</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Select a student</t>
+          <t>Check out a student with pending fee</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>Preview shows To, subject and the text with that student's amounts</t>
+          <t>Still listed as '(left)'</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -5233,22 +5233,22 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Change text for this sending</t>
+          <t>Tick and send</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Edit the message &gt; Send</t>
+          <t>Tick 2 students &gt; Send Reminder (2) &gt; confirm</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>Changed text sent; saved default unchanged</t>
+          <t>2 emails with total, paid, pending and invoice PDF; copy to admin; Last reminder date shown</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -5273,22 +5273,22 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Save as default</t>
+          <t>Father, else mother</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Edit &gt; Save as Default; then Saved Text</t>
+          <t>Student without father email but with mother email</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>Text kept for next time; Saved Text reloads it</t>
+          <t>Email to the mother; 'Mother: ...' shown</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -5313,22 +5313,22 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Unknown field</t>
+          <t>No parent email</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Type {Overdue} in the text &gt; Send or Save</t>
+          <t>Tick a student with no father or mother email &gt; Send</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>Error listing the available fields</t>
+          <t>Shown in red; listed as a problem; others sent</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -5353,22 +5353,22 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Never automatic</t>
+          <t>Select All / Clear</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Leave the program open for a day</t>
+          <t>Select All, then Clear</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>No reminder is sent unless the admin clicks Send</t>
+          <t>All emailable students ticked, then none; button count updates</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G117" s="10" t="inlineStr">
@@ -5393,22 +5393,22 @@
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Record payment</t>
+          <t>Preview</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Select a student &gt; Record Payment</t>
+          <t>Select a student</t>
         </is>
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>Payment recorded; amounts update</t>
+          <t>Preview shows To, subject and the text with that student's amounts</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -5433,17 +5433,17 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Export PDF</t>
+          <t>Change text for this sending</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Export PDF</t>
+          <t>Edit the message &gt; Send</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>PDF of the list with totals and page numbers</t>
+          <t>Changed text sent; saved default unchanged</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
@@ -5468,27 +5468,27 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Fee Reminders</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Test email</t>
+          <t>Save as default</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Email Settings &gt; app password &gt; Send test to address &gt; Send Test Email</t>
+          <t>Edit &gt; Save as Default; then Saved Text</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>'Test email sent'; email arrives</t>
+          <t>Text kept for next time; Saved Text reloads it</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -5508,27 +5508,27 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Fee Reminders</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Wrong app password</t>
+          <t>Unknown field</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Enter a wrong app password &gt; Send Test Email</t>
+          <t>Type {Overdue} in the text &gt; Send or Save</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>Message 'Gmail did not accept the sender address and app password'</t>
+          <t>Error listing the available fields</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -5548,22 +5548,22 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Fee Reminders</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>No internet</t>
+          <t>Never automatic</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Disconnect internet &gt; send</t>
+          <t>Leave the program open for a day</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>Message 'Could not connect to smtp.gmail.com'</t>
+          <t>No reminder is sent unless the admin clicks Send</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
@@ -5588,27 +5588,27 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Fee Reminders</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Email invoice</t>
+          <t>Record payment</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Invoices &gt; Email</t>
+          <t>Select a student &gt; Record Payment</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>Father (or mother) receives the invoice PDF with paid and pending; admin gets a copy</t>
+          <t>Payment recorded; amounts update</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -5628,27 +5628,27 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Fee Reminders</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Email receipt</t>
+          <t>Export PDF</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Payments &gt; Email Receipt</t>
+          <t>Export PDF</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>Father (or mother) receives the receipt PDF; admin copy</t>
+          <t>PDF of the list with totals and page numbers</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -5673,22 +5673,22 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Edit email text</t>
+          <t>Test email</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Edit Invoice email subject &gt; Save &gt; send</t>
+          <t>Email Settings &gt; app password &gt; Send test to address &gt; Send Test Email</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>New subject used; Restore Default works</t>
+          <t>'Test email sent'; email arrives</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -5713,22 +5713,22 @@
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Unknown field</t>
+          <t>Wrong app password</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Type {ReceiptNo} in Receipt email &gt; Save</t>
+          <t>Enter a wrong app password &gt; Send Test Email</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>Error listing the available fields</t>
+          <t>Message 'Gmail did not accept the sender address and app password'</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Email history</t>
+          <t>No internet</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Email Settings &gt; Email history</t>
+          <t>Disconnect internet &gt; send</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>All sent and failed emails; failed in red with reason</t>
+          <t>Message 'Could not connect to smtp.gmail.com'</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Not set up</t>
+          <t>Email invoice</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Send an email before entering the app password</t>
+          <t>Invoices &gt; Email</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>Message to set up Email Settings first</t>
+          <t>Father (or mother) receives the invoice PDF with paid and pending; admin gets a copy</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -5828,22 +5828,22 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Figures</t>
+          <t>Email receipt</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Compare with Students, Rooms, Invoices, Payments, Fee Reminders</t>
+          <t>Payments &gt; Email Receipt</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>Students, beds, fees this year, received this month and year, pending match</t>
+          <t>Father (or mother) receives the receipt PDF; admin copy</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
@@ -5868,22 +5868,22 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Edit email text</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Record a payment today &gt; reopen Dashboard</t>
+          <t>Edit Invoice email subject &gt; Save &gt; send</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>Current month bar and Received increase; hover shows exact amount</t>
+          <t>New subject used; Restore Default works</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
@@ -5908,22 +5908,22 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Unknown field</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Check the three lists</t>
+          <t>Type {ReceiptNo} in Receipt email &gt; Save</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>5 highest pending fees, latest payments, latest check-ins</t>
+          <t>Error listing the available fields</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
@@ -5948,22 +5948,22 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Other hostel</t>
+          <t>Email history</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Switch hostel</t>
+          <t>Email Settings &gt; Email history</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>All figures change to that hostel</t>
+          <t>All sent and failed emails; failed in red with reason</t>
         </is>
       </c>
       <c r="F132" s="9" t="inlineStr">
@@ -5988,27 +5988,27 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Student list</t>
+          <t>Not set up</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Reports &gt; Student list &gt; Active &gt; Show</t>
+          <t>Send an email before entering the app password</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
         <is>
-          <t>Active students with masked Aadhaar; total count</t>
+          <t>Message to set up Email Settings first</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -6028,22 +6028,22 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Room occupancy</t>
+          <t>Figures</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Room occupancy &gt; Show</t>
+          <t>Compare with Students, Rooms, Invoices, Payments, Fee Reminders</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>Each room, beds, occupied, free, students (no rent); totals match Rooms screen</t>
+          <t>Students, beds, fees this year, received this month and year, pending match</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr">
@@ -6068,27 +6068,27 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Payments received</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Dates of the month &gt; Show</t>
+          <t>Record a payment today &gt; reopen Dashboard</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>Payments with a total per day, per method and grand total</t>
+          <t>Current month bar and Received increase; hover shows exact amount</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -6108,27 +6108,27 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Fees report</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Fees (invoices) &gt; Year 2026-27, status Unpaid</t>
+          <t>Check the three lists</t>
         </is>
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>Only unpaid fees of that year with rent, transport, total, paid, pending; totals</t>
+          <t>5 highest pending fees, latest payments, latest check-ins</t>
         </is>
       </c>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -6148,22 +6148,22 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Export PDF</t>
+          <t>Other hostel</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Any report &gt; Export PDF</t>
+          <t>Switch hostel</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>PDF opens, headings on every page, page numbers</t>
+          <t>All figures change to that hostel</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>Export Excel</t>
+          <t>Student list</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Any report &gt; Export Excel</t>
+          <t>Reports &gt; Student list &gt; Active &gt; Show</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>Excel opens; amounts are numbers in rupees, dates are dates, filters work</t>
+          <t>Active students with masked Aadhaar; total count</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Wrong dates</t>
+          <t>Room occupancy</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>From after To</t>
+          <t>Room occupancy &gt; Show</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>Error message</t>
+          <t>Each room, beds, occupied, free, students (no rent); totals match Rooms screen</t>
         </is>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>Pending fees report</t>
+          <t>Payments received</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Pending fees &gt; Show</t>
+          <t>Dates of the month &gt; Show</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>Student lines with total, paid, pending, then their invoices</t>
+          <t>Payments with a total per day, per method and grand total</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G140" s="10" t="inlineStr">
@@ -6308,27 +6308,27 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>Backup / Restore</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>Backup now</t>
+          <t>Fees report</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Backup / Restore &gt; Backup Now</t>
+          <t>Fees (invoices) &gt; Year 2026-27, status Unpaid</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>Zip in Backups listed as 'Backup Now'; contains database, photos, documents</t>
+          <t>Only unpaid fees of that year with rent, transport, total, paid, pending; totals</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G141" s="10" t="inlineStr">
@@ -6348,27 +6348,27 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>Backup / Restore</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Daily automatic backup</t>
+          <t>Export PDF</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Close the program (first time today)</t>
+          <t>Any report &gt; Export PDF</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>Automatic backup made; only one per day</t>
+          <t>PDF opens, headings on every page, page numbers</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G142" s="10" t="inlineStr">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>Backup / Restore</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>Second copy folder</t>
+          <t>Export Excel</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Choose a USB / Google Drive folder &gt; Backup Now</t>
+          <t>Any report &gt; Export Excel</t>
         </is>
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>Zip also in that folder</t>
+          <t>Excel opens; amounts are numbers in rupees, dates are dates, filters work</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
@@ -6428,22 +6428,22 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>Backup / Restore</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>Second folder missing</t>
+          <t>Wrong dates</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Remove the USB &gt; Backup Now</t>
+          <t>From after To</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>Backup made; message that the second copy failed</t>
+          <t>Error message</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
@@ -6468,27 +6468,27 @@
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>Backup / Restore</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Restore</t>
+          <t>Pending fees report</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Add a test hostel &gt; Restore an older backup &gt; confirm</t>
+          <t>Pending fees &gt; Show</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>Program restarts; test hostel gone; 'Before a restore' backup created</t>
+          <t>Student lines with total, paid, pending, then their invoices</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G145" s="10" t="inlineStr">
@@ -6513,22 +6513,22 @@
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>Undo restore</t>
+          <t>Backup now</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Restore the 'Before a restore' backup</t>
+          <t>Backup / Restore &gt; Backup Now</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>Data from before the restore is back</t>
+          <t>Zip in Backups listed as 'Backup Now'; contains database, photos, documents</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G146" s="10" t="inlineStr">
@@ -6553,22 +6553,22 @@
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Wrong file</t>
+          <t>Daily automatic backup</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Restore From File &gt; choose a non-backup zip</t>
+          <t>Close the program (first time today)</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>Clear error; nothing changed</t>
+          <t>Automatic backup made; only one per day</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G147" s="10" t="inlineStr">
@@ -6588,22 +6588,22 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Backup / Restore</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>Database check</t>
+          <t>Second copy folder</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Application Settings &gt; Test Database</t>
+          <t>Choose a USB / Google Drive folder &gt; Backup Now</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>All steps pass</t>
+          <t>Zip also in that folder</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
@@ -6628,22 +6628,22 @@
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Backup / Restore</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>User guide</t>
+          <t>Second folder missing</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Application Settings &gt; User Guide</t>
+          <t>Remove the USB &gt; Backup Now</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>User guide opens</t>
+          <t>Backup made; message that the second copy failed</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
@@ -6668,27 +6668,27 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Backup / Restore</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>Menu fits screen</t>
+          <t>Restore</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>Laptop 1366 x 768, maximised</t>
+          <t>Add a test hostel &gt; Restore an older backup &gt; confirm</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>No scroll bar in the left menu</t>
+          <t>Program restarts; test hostel gone; 'Before a restore' backup created</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G150" s="10" t="inlineStr">
@@ -6708,22 +6708,22 @@
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Backup / Restore</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>No technical errors shown</t>
+          <t>Undo restore</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Cause errors (e.g. open the database in Access and save)</t>
+          <t>Restore the 'Before a restore' backup</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>Friendly message; details in Logs</t>
+          <t>Data from before the restore is back</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
@@ -6748,27 +6748,27 @@
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>Uninstall</t>
+          <t>Backup / Restore</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>Uninstall keeps data</t>
+          <t>Wrong file</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>Settings &gt; Apps &gt; Uninstall</t>
+          <t>Restore From File &gt; choose a non-backup zip</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>Program removed; Database, Photos, Documents, Invoices, Receipts, Reports, Agreements, Backups kept</t>
+          <t>Clear error; nothing changed</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G152" s="10" t="inlineStr">
@@ -6788,27 +6788,27 @@
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>Uninstall</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>Reinstall uses old data</t>
+          <t>Database check</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Install again into C:\HostelManagement</t>
+          <t>Application Settings &gt; Test Database</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>All data is back</t>
+          <t>All steps pass</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G153" s="10" t="inlineStr">
@@ -6820,9 +6820,209 @@
       <c r="I153" s="11" t="inlineStr"/>
       <c r="J153" s="10" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>TC-153</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>Application Settings</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>User guide</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>Application Settings &gt; User Guide</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>User guide opens</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr"/>
+      <c r="I154" s="11" t="inlineStr"/>
+      <c r="J154" s="10" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>TC-154</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Menu fits screen</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>Laptop 1366 x 768, maximised</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>No scroll bar in the left menu</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr"/>
+      <c r="I155" s="11" t="inlineStr"/>
+      <c r="J155" s="10" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>TC-155</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>No technical errors shown</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>Cause errors (e.g. open the database in Access and save)</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>Friendly message; details in Logs</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="inlineStr"/>
+      <c r="I156" s="11" t="inlineStr"/>
+      <c r="J156" s="10" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>TC-156</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>Uninstall</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>Uninstall keeps data</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>Settings &gt; Apps &gt; Uninstall</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr">
+        <is>
+          <t>Program removed; Database, Photos, Documents, Invoices, Receipts, Reports, Agreements, Backups kept</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr"/>
+      <c r="I157" s="11" t="inlineStr"/>
+      <c r="J157" s="10" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>TC-157</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>Uninstall</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Reinstall uses old data</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>Install again into C:\HostelManagement</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>All data is back</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="inlineStr"/>
+      <c r="I158" s="11" t="inlineStr"/>
+      <c r="J158" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J153"/>
-  <conditionalFormatting sqref="G2:G153">
+  <autoFilter ref="A1:J158"/>
+  <conditionalFormatting sqref="G2:G158">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -6834,7 +7034,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not run,Pass,Fail,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7699,23 +7899,23 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A2)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A2)</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A2,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A2,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D2" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A2,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A2,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E2" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A2,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A2,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F2" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A2,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A2,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G2" s="14">
@@ -7730,23 +7930,23 @@
         </is>
       </c>
       <c r="B3" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A3)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A3)</f>
         <v/>
       </c>
       <c r="C3" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A3,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A3,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D3" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A3,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A3,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A3,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A3,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F3" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A3,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A3,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G3" s="14">
@@ -7761,23 +7961,23 @@
         </is>
       </c>
       <c r="B4" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A4)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A4)</f>
         <v/>
       </c>
       <c r="C4" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A4,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A4,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A4,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A4,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A4,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A4,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F4" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A4,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A4,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G4" s="14">
@@ -7792,23 +7992,23 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A5)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A5)</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A5,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A5,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A5,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A5,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A5,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A5,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A5,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A5,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G5" s="14">
@@ -7823,23 +8023,23 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A6)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A6)</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A6,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A6,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A6,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A6,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A6,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A6,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A6,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A6,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G6" s="14">
@@ -7854,23 +8054,23 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A7)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A7)</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A7,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A7,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A7,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A7,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A7,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A7,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A7,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A7,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G7" s="14">
@@ -7885,23 +8085,23 @@
         </is>
       </c>
       <c r="B8" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A8)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A8)</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A8,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A8,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A8,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A8,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A8,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A8,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A8,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A8,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G8" s="14">
@@ -7916,23 +8116,23 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A9)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A9)</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A9,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A9,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A9,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A9,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A9,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A9,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A9,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A9,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G9" s="14">
@@ -7947,23 +8147,23 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A10)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A10)</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A10,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A10,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A10,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A10,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A10,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A10,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A10,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A10,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G10" s="14">
@@ -7978,23 +8178,23 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A11)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A11)</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A11,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A11,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A11,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A11,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A11,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A11,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A11,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A11,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G11" s="14">
@@ -8009,23 +8209,23 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A12)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A12)</f>
         <v/>
       </c>
       <c r="C12" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A12,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A12,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A12,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A12,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A12,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A12,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A12,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A12,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G12" s="14">
@@ -8040,23 +8240,23 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A13)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A13)</f>
         <v/>
       </c>
       <c r="C13" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A13,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A13,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A13,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A13,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A13,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A13,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A13,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A13,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G13" s="14">
@@ -8071,23 +8271,23 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A14)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A14)</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A14,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A14,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A14,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A14,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A14,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A14,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F14" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A14,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A14,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G14" s="14">
@@ -8102,23 +8302,23 @@
         </is>
       </c>
       <c r="B15" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A15)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A15)</f>
         <v/>
       </c>
       <c r="C15" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A15,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A15,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A15,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A15,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A15,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A15,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A15,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A15,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G15" s="14">
@@ -8133,23 +8333,23 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A16)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A16)</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A16,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A16,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A16,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A16,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A16,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A16,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A16,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A16,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G16" s="14">
@@ -8164,23 +8364,23 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A17)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A17)</f>
         <v/>
       </c>
       <c r="C17" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A17,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A17,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A17,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A17,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A17,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A17,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A17,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A17,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G17" s="14">
@@ -8195,23 +8395,23 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A18)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A18)</f>
         <v/>
       </c>
       <c r="C18" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A18,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A18,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A18,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A18,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A18,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A18,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A18,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A18,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G18" s="14">
@@ -8226,23 +8426,23 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A19)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A19)</f>
         <v/>
       </c>
       <c r="C19" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A19,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A19,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A19,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A19,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A19,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A19,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A19,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A19,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G19" s="14">
@@ -8257,23 +8457,23 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A20)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A20)</f>
         <v/>
       </c>
       <c r="C20" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A20,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A20,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A20,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A20,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A20,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A20,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A20,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A20,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G20" s="14">
@@ -8288,23 +8488,23 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$153,A21)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$158,A21)</f>
         <v/>
       </c>
       <c r="C21" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A21,'Test Cases'!$G$2:$G$153,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A21,'Test Cases'!$G$2:$G$158,"Pass")</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A21,'Test Cases'!$G$2:$G$153,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A21,'Test Cases'!$G$2:$G$158,"Fail")</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A21,'Test Cases'!$G$2:$G$153,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A21,'Test Cases'!$G$2:$G$158,"Blocked")</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$153,$A21,'Test Cases'!$G$2:$G$153,"Not run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$158,$A21,'Test Cases'!$G$2:$G$158,"Not run")</f>
         <v/>
       </c>
       <c r="G21" s="14">
